--- a/vse-loti/339707952/spec-339707952.xlsx
+++ b/vse-loti/339707952/spec-339707952.xlsx
@@ -60,13 +60,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -434,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -455,35 +454,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -495,48 +499,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Набор для донорской крови, четырехкамерный</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
-        <v>5522370</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>еристики не может изменяться участником закупки Пластиковые зажимы на магистралях</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>5522370</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="4" t="n">
         <v>5522370</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Источник: Obosnovanie NMTs .txt</t>
+          <t>Источник: spec-339707952.txt</t>
         </is>
       </c>
     </row>
